--- a/data/raw/Metro_Route.xlsx
+++ b/data/raw/Metro_Route.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harsh\Desktop\Crowd Prediction and Staff Allocation System\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD639C1-7887-42BE-A882-2466D0E1AE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9168B41-471A-46D5-BEB9-2954CE0EF410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{33CBD1A9-71FE-47CF-82C5-7D4EFAB77AD0}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="119">
   <si>
     <t>Station Code</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>JAI HIND BIMANBANDAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRAL </t>
   </si>
 </sst>
 </file>
@@ -1369,7 +1372,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
